--- a/examples/lci-pass_cars.xlsx
+++ b/examples/lci-pass_cars.xlsx
@@ -8,14 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/trails/examples/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA29452-3ABD-364A-969E-D81A503C4379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0155B67-37CB-EC43-BF1E-11D231BFF94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="36780" yWindow="520" windowWidth="25800" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="passenger cars" sheetId="1" r:id="rId1"/>
-    <sheet name="biomass" sheetId="2" r:id="rId2"/>
-    <sheet name="daccs" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="111">
   <si>
     <t>Database</t>
   </si>
@@ -364,7 +362,10 @@
     <t>matrix</t>
   </si>
   <si>
-    <t>Here, the matrix-stored value is used, instead of porting the value and distirbuting it over years.</t>
+    <t>Here, the matrix-stored value is used, instead of porting the value and distirbuting it over years. Also, we indicate year-specific values. When absent, values under "amount" apply.</t>
+  </si>
+  <si>
+    <t>temporal_distribution: 2 = lognormal, 3 = normal, 4 = uniform and 5 = triangular.</t>
   </si>
 </sst>
 </file>
@@ -723,9 +724,7 @@
   <cols>
     <col min="1" max="1" width="49.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.1640625" customWidth="1"/>
-    <col min="3" max="4" width="6.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="6.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.5" customWidth="1"/>
     <col min="11" max="11" width="26.5" customWidth="1"/>
     <col min="12" max="12" width="18.5" bestFit="1" customWidth="1"/>
@@ -1394,6 +1393,9 @@
       <c r="P24">
         <v>-1</v>
       </c>
+      <c r="R24" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
@@ -3186,22 +3188,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80C876FE-44EF-5B45-94D8-BBE1EF407674}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B62C105-C6C4-0C43-B446-11A21C4C2EC8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>